--- a/templates/lifestyle/habit-tracker.xlsx
+++ b/templates/lifestyle/habit-tracker.xlsx
@@ -6,12 +6,26 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Habits" sheetId="1" r:id="rId1"/>
+    <sheet name="Habits" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="MonthDays">Habits!$C$5</definedName>
     <definedName name="MonthStart">Habits!$C$4</definedName>
   </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -137,11 +151,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF6DB"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -196,7 +212,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -235,7 +251,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid"/>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF2F7D4F"/>
@@ -250,6 +274,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF5F7FA"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -260,6 +285,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDDF1E4"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -454,7 +480,6 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle"/>
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -472,7 +497,6 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle"/>
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -490,10 +514,20 @@
     <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="9.6015625" customWidth="1"/>
-    <col min="4" max="34" width="3.3984375" customWidth="1"/>
+    <col min="4" max="4" width="3.4296875" bestFit="1"/>
+    <col min="5" max="5" width="3.5703125" bestFit="1"/>
+    <col min="6" max="11" width="3.4296875" bestFit="1"/>
+    <col min="12" max="12" width="3.5703125" bestFit="1"/>
+    <col min="13" max="18" width="3.4296875" bestFit="1"/>
+    <col min="19" max="19" width="3.5703125" bestFit="1"/>
+    <col min="20" max="25" width="3.4296875" bestFit="1"/>
+    <col min="26" max="26" width="3.5703125" bestFit="1"/>
+    <col min="27" max="32" width="3.4296875" bestFit="1"/>
+    <col min="33" max="33" width="3.5703125" bestFit="1"/>
+    <col min="34" max="34" width="3.4296875" bestFit="1"/>
     <col min="35" max="35" width="6.3984375" customWidth="1"/>
     <col min="36" max="36" width="7.6015625" customWidth="1"/>
-    <col min="37" max="37" width="9.6015625" customWidth="1"/>
+    <col min="37" max="37" width="9.5703125" bestFit="1"/>
   </cols>
   <sheetData>
     <row r="2" x14ac:dyDescent="0.25">
@@ -1304,7 +1338,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" x14ac:dyDescent="0.25" thickBot="1">
       <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
@@ -1446,27 +1480,74 @@
         <v>0.5784313725490197</v>
       </c>
     </row>
+    <row r="17" x14ac:dyDescent="0.25" thickTop="1"/>
   </sheetData>
+  <conditionalFormatting sqref="D6:AH7">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(ISNUMBER(D$7),MonthStart+D$7-1=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:AH16">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AK8:AK16">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="dataBar" priority="3">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF8CCB9E"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1B9D7C70-0CB1-43AA-8770-3432A883994B}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>AND(ISNUMBER(AK8),AK8&gt;=1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:AH6">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>OR(D6="Sa",D6="Su")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:AH15">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>D$7=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:AH15">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>LOWER(D8)="x"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1B9D7C70-0CB1-43AA-8770-3432A883994B}">
+            <x14:dataBar negativeBarColorSameAsPositive="1">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AK8:AK16</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>